--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_03_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_03_20_Cau.xlsx
@@ -1183,7 +1183,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một posting gần tên chưa chắc cùng population tuyển dụng.</t>
+          <t>Để so sánh yêu cầu tuyển dụng Data Engineer cấp độ Junior tại Việt Nam trong quý hiện tại, chỉ lấy các bài đăng đúng nhóm đối tượng: (a) Junior Data Engineer tại TP.HCM đăng 2 tuần trước, (b) Junior Data Engineer tại Hà Nội đăng 1 tháng trước, (e) Junior Data Engineer làm remote tại Việt Nam đăng 3 tuần trước.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_03_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_03_20_Cau.xlsx
@@ -624,10 +624,22 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Cost win không bù quality guardrail breach.
-Phân tích theo nguyên lý thiết kế: Cost win không bù quality guardrail breach.</t>
+- 1.0đ: Đưa ra phán quyết dứt khoát: REJECT / ROLLBACK cấu hình cache candidate ngay lập tức.
+- 1.0đ: Phân tích sâu sắc vi phạm rào cản: stale-answer rate 1.8% vượt xa ngưỡng trần cho phép (&lt;=0.5%).
+- 1.0đ: Khẳng định nguyên tắc đạo đức và kỹ nghệ: chiến thắng chi phí không thể bù đắp cho sự suy giảm rào cản chất lượng.
+- 1.0đ: Thiết lập kế hoạch khắc phục khoa học (Event-driven cache invalidation, rút ngắn TTL, thử nghiệm lại trên Canary).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phán quyết Kỹ thuật (Technical Verdict): **REJECT / ROLLBACK CANDIDATE CACHE NGAY LẬP TỨC (BÁC BỎ VÀ HOÀN NGUYÊN)**.
+- **Lập luận Phán quyết**: Mặc dù giải pháp Cache candidate mang lại chiến thắng lớn về mặt tài chính (giảm tới 25% số lượng cuộc gọi model tốn kém), nhưng nó đã làm **TỶ LỆ CÂU TRẢ LỜI LỖI THỜI (STALE-ANSWER RATE) TĂNG VỌT TỪ 0.2% LÊN 1.8%**.
+- **Vi phạm Rào cản An toàn Bất biến (Guardrail Breach)**: Quy chuẩn rào cản an toàn quy định nghiêm ngặt: `stale_answer_rate &lt;= 0.5%`. Mức 1.8% đã vượt quá ngưỡng trần cho phép tới gần 4 lần! Trong kỹ nghệ phần mềm và AI, **khoản tiết kiệm chi phí không bao giờ được phép dùng để đánh đổi cho sự sụp đổ chất lượng và thông tin sai lệch cho khách hàng**.
+2. Kế hoạch Kiểm chứng và Hiệu chỉnh Kỹ thuật (Verification &amp; Remediation Plan):
+- **Hành động 1: Hoàn nguyên Khẩn cấp (Immediate Rollback)**: Tắt cờ cache candidate, khôi phục cấu hình baseline cũ để đưa tỷ lệ stale-answer về mức an toàn 0.2% trong vòng 5 phút.
+- **Hành động 2: Tinh chỉnh Cơ chế Hủy Cache theo Sự kiện (Event-driven Cache Invalidation)**: Thay vì dựa vào thời gian sống cố định (Fixed TTL), xây dựng cơ chế Webhook Invalidation: Bất cứ khi nào tài liệu trong kho dữ liệu được cập nhật, hệ thống tự động xóa khóa cache tương ứng ngay lập tức.
+- **Hành động 3: Thử nghiệm lại trên Lát cắt Canary Nhỏ (Canary Re-verification)**: Giảm TTL xuống mức an toàn (ví dụ từ 10m xuống 2m); chạy thử nghiệm trên 5% lưu lượng trong 72 giờ. Chỉ chấp thuận release khi đồng thời thỏa mãn: Giảm model calls $&gt; 15\%$ VÀ `stale_answer_rate &lt;= 0.3\%`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Rào cản An toàn Bất khả Xâm phạm trong Tối ưu hóa (Guardrails Trump Cost Wins): Một hệ thống tiết kiệm được 25% chi phí nhưng cung cấp thông tin sai lệch cho 1.8% khách hàng sẽ phá hủy uy tín thương hiệu và dẫn đến khiếu nại pháp lý đắt đỏ hơn nhiều. Khi một chỉ số Guardrail bị vi phạm, phán quyết kỹ thuật chỉ có một: Bác bỏ và Hoàn nguyên. Chỉ được tái triển khai khi đã bổ sung cơ chế hủy cache thông minh (Event-driven Invalidation) để bảo vệ tính cập nhật của dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Canarying Releases &amp; Phil Karlton: Two Hard Things in Computer Science (Cache Invalidation)</t>
         </is>
       </c>
     </row>
@@ -706,10 +718,27 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giữ đúng population và loại measure.
-Phân tích theo nguyên lý thiết kế: Giữ đúng population và loại measure.</t>
+- 1.0đ: Xác lập chuẩn xác biến số đo lường là Kỳ vọng Chủ quan của Nhà quản lý (Subjective Expectation) trên mẫu số N=500.
+- 1.0đ: Chỉ ra và giải thích rõ Khẳng định Cấm 1 (đánh tráo kỳ vọng tương lai với thực tế hiện tại).
+- 1.0đ: Chỉ ra và giải thích rõ Khẳng định Cấm 2 (khái quát hóa sai từ 500 manager sang toàn bộ người lao động).
+- 1.0đ: Thể hiện nguyên tắc khoa học về tính đại diện của mẫu và ranh giới suy diễn dữ liệu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết lập Biến số Đo lường (Variable Operationalization) và Hai Khẳng định Tuyệt đối Không Được Phép (Forbidden Claims):
+1. **Xác lập Bản chất Biến số Đo lường (Variable Operationalization)**:
+- **Tên biến số**: `manager_expectation_ai_role_expansion`.
+- **Bản chất đo lường (Construct)**: Đây là một **Biến số Ý kiến Chủ quan / Kỳ vọng Hướng tới Tương lai (Subjective Attitudinal Expectation)** của nhóm người tham gia khảo sát, đo lường nhận thức (perception) tại thời điểm khảo sát.
+- **Mẫu số &amp; Quần thể (Denominator &amp; Population)**: $N = 500$ nhà quản lý (Manager Respondents) tham gia trả lời khảo sát cụ thể này.
+2. **Hai Khẳng định Tuyệt đối KHÔNG ĐƯỢC PHÉP (Two Forbidden Overclaims)**:
+- **Khẳng định Cấm 1: Đánh tráo Kỳ vọng Tương lai thành Thực tế Hiện tại (Conflating Expectation with Factual Reality)**:
+  + *Tuyên bố vi phạm*: 'AI Agents đã mở rộng vai trò công việc cho 60% nhân viên tại các doanh nghiệp.'
+  + *Lý do cấm*: Biến số chỉ đo lường sự kỳ vọng/hy vọng của nhà quản lý ('expect'), hoàn toàn không đo lường thực tế khách quan xem các AI agent đã thực sự làm được điều đó hay chưa.
+- **Khẳng định Cấm 2: Khái quát hóa Sai Quần thể (Overgeneralizing Population from Managers to All Workers)**:
+  + *Tuyên bố vi phạm*: '60% người lao động và nhân viên toàn cầu tin rằng AI sẽ mở rộng công việc của họ.'
+  + *Lý do cấm*: Mẫu số khảo sát chỉ gồm 500 nhà quản lý ($N=500$ managers). Góc nhìn của cấp quản lý thường lạc quan thái quá về công nghệ và hoàn toàn không đại diện cho quan điểm, tâm tư hay thực trạng của hàng triệu nhân viên cấp dưới trực tiếp.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Liêm chính Dữ liệu trong Phân tích Thị trường (Market Measure Identification &amp; Anti-overclaiming): Báo cáo truyền thông thường cố tình 'giật tít' đánh tráo khái niệm: biến 60% ý kiến kỳ vọng của 500 ông sếp thành '60% công việc thực tế đã thay đổi'. Một nhà khoa học dữ liệu và kỹ sư trưởng phải giữ vững ranh giới đo lường: biến số đo cái gì thì chỉ được báo cáo đúng cái đó trong phạm vi mẫu số (denominator) đã xác định.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+American Association for Public Opinion Research (AAPOR) Best Practices &amp; Darrell Huff: How to Lie with Statistics</t>
         </is>
       </c>
     </row>
@@ -740,10 +769,28 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Card cần trả lời khi nào, ở đâu, ai, bao nhiêu và thu bằng cách nào.
-Phân tích theo nguyên lý thiết kế: Card cần trả lời khi nào, ở đâu, ai, bao nhiêu và thu bằng cách nào.</t>
+- 1.0đ: Lập đầy đủ 5 thành phần của Methodology Card (Thời gian, Địa lý, Kích thước mẫu N=2000, Đối tượng knowledge workers, Phương thức online).
+- 1.0đ: Phân tích vi phạm phân khúc nghề nghiệp (knowledge workers không đại diện cho toàn bộ lao động).
+- 1.0đ: Phân tích vi phạm thiên vị tiếp cận số và sự khác biệt kinh tế đặc thù của Việt Nam.
+- 1.0đ: Bác bỏ hoàn toàn việc ngoại suy thời gian vô căn cứ từ năm 2026 sang năm 2030.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Lập Thẻ Phương pháp luận Thị trường (Market Methodology Card) và Ranh giới Giới hạn Khái quát hóa (Generalization Limits):
+1. **Thẻ Phương pháp luận (Market Methodology Card)**:
+- **Thời gian công bố (When)**: Tháng 05/2026.
+- **Phương thức thu thập (How)**: Khảo sát trực tuyến có trọng số (Online Survey with Demographic Weighting).
+- **Kích thước mẫu (How Many)**: $N = 2.000$ người trả lời.
+- **Đối tượng khảo sát (Who)**: Lao động tri thức (Knowledge Workers) có sử dụng Internet.   *(Lưu ý: Mẫu loại trừ hoàn toàn lao động phổ thông, lao động chân tay và người không tiếp cận Internet)*.
+- **Phạm vi địa lý (Where)**: Phân bổ trên 10 thị trường quốc tế.
+2. **Phê phán Ý định Áp dụng cho 'Mọi Lao động Việt Nam năm 2030' (Generalization Audit)**:
+Ý định áp đặt kết quả này cho toàn bộ lực lượng lao động Việt Nam vào năm 2030 là **HOÀN TOÀN SAI LẦM VÀ VÔ GIÁ TRỊ VỀ MẶT KHOA HỌC** do 4 vi phạm giới hạn nghiêm trọng:
+- **Vi phạm Phân khúc Nghề nghiệp (Occupational Bias)**: Báo cáo chỉ khảo sát Knowledge Workers (chiếm tỷ lệ nhỏ trong lực lượng lao động), hoàn toàn không đại diện cho hàng chục triệu lao động trong ngành nông nghiệp, sản xuất dệt may, xây dựng và dịch vụ truyền thống tại Việt Nam.
+- **Vi phạm Thiên vị Tiếp cận Số (Digital Access Selection Bias)**: Khảo sát làm online nên loại bỏ những người không dùng internet, tạo ra bức tranh thiên vị công nghệ màu hồng.
+- **Vi phạm Địa lý và Thể chế (Geographic &amp; Economic Specificity)**: Dữ liệu của 10 thị trường nước ngoài không phản ánh cơ cấu kinh tế, mức lương và chính sách việc làm đặc thù của Việt Nam.
+- **Vi phạm Dự báo Thời gian (Temporal Leap 2026 -&gt; 2030)**: Không thể dùng dữ liệu cắt ngang (Cross-sectional) tại một thời điểm năm 2026 để ngoại suy cơ học cho tương lai 4 năm sau mà không có mô hình chuỗi thời gian.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thẻ Phương pháp luận trong Nghiên cứu Thị trường (Methodology Card &amp; External Validity): Phương pháp thu thập dữ liệu quyết định giới hạn khái quát hóa (Methodology dictates generalization). Một báo cáo khảo sát 2.000 người làm việc văn phòng trên mạng vào năm 2026 chỉ có giá trị cho chính tập đối tượng đó. Đem số liệu này để hoạch định chiến lược cho toàn bộ người lao động Việt Nam năm 2030 là sự ngụy tạo dữ liệu nguy hiểm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+AAPOR Transparency Initiative &amp; World Bank Guidelines for Labor Market Analysis</t>
         </is>
       </c>
     </row>
@@ -774,10 +821,28 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Method quyết định generalization chứ không chỉ n của toàn report.
-Phân tích theo nguyên lý thiết kế: Method quyết định generalization chứ không chỉ n của toàn report.</t>
+- 1.0đ: Phân tích giới hạn thiên vị tự báo cáo (Self-reporting / Prestige bias) làm sai lệch số liệu danh nghĩa.
+- 1.0đ: Chỉ ra lỗi phương pháp luận khi loại bỏ missing salary (Missing Not At Random / MNAR trap).
+- 1.0đ: Phân tích hiện tượng mất cân bằng cỡ mẫu khi chia nhỏ theo thành phố và vị trí chuyên môn.
+- 1.0đ: Phê phán việc so sánh lương danh nghĩa mà không chuẩn hóa theo chi phí sinh hoạt giữa các thành phố.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Kiểm toán Giới hạn Phương pháp luận (Methodological Audit Limitations) khi So sánh Lương giữa các Thành phố:
+1. **Bản chất của Tập Dữ liệu Khảo sát**:
+- Quy mô: $N = 2.500$ người trả lời tại 3 thành phố (TP.HCM, Hà Nội, Đà Nẵng), thu thập năm 2025.
+- Phương thức: Thu nhập tự báo cáo (Self-reported Compensation) và áp dụng cơ chế xóa bỏ các bản ghi thiếu thông tin lương (Listwise Deletion).
+2. **Bốn Giới hạn Kiểm toán Cốt tử khi So sánh giữa các Thành phố (Four Critical Audit Limitations)**:
+- **Giới hạn 1: Thiên vị Tự Báo cáo và Thiên vị Uy tín (Self-reporting &amp; Social Desirability Bias)**:
+  + Dữ liệu lương do ứng viên tự điền thường bị thổi phồng (over-reporting) để nâng cao giá trị bản thân,   hoặc chỉ những người có mức lương cao đáng tự hào mới sẵn sàng chia sẻ.   Mức độ thiên vị này có thể khác nhau giữa các nền văn hóa vùng miền của 3 thành phố, làm sai lệch bảng so sánh.
+- **Giới hạn 2: Cạm bẫy Xóa Dữ liệu Khuyết Thiếu Không Ngẫu Nhiên (Missing-Not-At-Random - MNAR Bias)**:
+  + Việc tự ý loại bỏ các ca không điền lương (missing salary) là sai lầm thống kê nghiêm trọng.   Người từ chối tiết lộ lương thường rơi vào hai thái cực: người có lương quá thấp (ngại chia sẻ) hoặc người có lương cực cao (bảo mật nghiêm ngặt).   Loại bỏ họ làm méo mó hoàn toàn phân phối lương thực tế của từng thành phố.
+- **Giới hạn 3: Mất Cân bằng Phân bổ Cỡ mẫu theo Phân khúc (Unbalanced Sample Slices)**:
+  + Tổng số 2.500 mẫu có thể phân bổ 80% ở TP.HCM ($n=2.000$), trong khi Đà Nẵng chỉ có vỏn vẹn 100 mẫu.   Khi bóc tách theo vị trí (ví dụ: Senior AI Engineer tại Đà Nẵng), số mẫu có thể $&lt; 5$, làm cho con số trung vị tại Đà Nẵng trở nên cực kỳ bất ổn định (unstable).
+- **Giới hạn 4: Bỏ qua Chỉ số Chi phí Sinh hoạt (Purchasing Power Parity / Cost-of-Living Neglect)**:
+  + So sánh con số lương danh nghĩa tuyệt đối (Nominal Salary) giữa TP.HCM và Đà Nẵng mà không chuẩn hóa theo chi phí sinh hoạt (tiền thuê nhà, dịch vụ)   là sự so sánh khập khiễng, không phản ánh đúng thu nhập thực tế (Real Income) của người lao động.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Kiểm toán Báo cáo Lương Thị trường (Salary Survey Methodological Audit): Các báo cáo lương tuyển dụng thường tạo ra ảo giác tin cậy nhờ con số tổng mẫu lớn (N=2.500). Tuy nhiên, khi phân rã để so sánh giữa các thành phố, các lỗi về tự báo cáo, xóa dữ liệu khuyết thiếu (MNAR) và kích thước mẫu nhỏ tại các thành phố vệ tinh sẽ bóp méo hoàn toàn sự thật. Nhận diện 4 giới hạn này bảo đảm doanh nghiệp không đưa ra các chính sách đãi ngộ sai lầm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Donald B. Rubin: Inference and Missing Data (Biometrika 1976) &amp; ILO (International Labour Organization) Wage Survey Methodologies</t>
         </is>
       </c>
     </row>
@@ -856,10 +921,20 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Comparable không đồng nghĩa precise.
-Phân tích theo nguyên lý thiết kế: Comparable không đồng nghĩa precise.</t>
+- 1.0đ: Khẳng định dứt khoát: KHÔNG được phép xếp hạng chắc chắn giữa hai thành phố.
+- 1.0đ: Phân tích sâu sắc sự bất ổn định thống kê của ô Hà Nội do cỡ mẫu quá nhỏ ($n=8 &lt; 10$).
+- 1.0đ: Vạch trần cạm bẫy 'cùng số trung vị' không đồng nghĩa với cùng mức độ tin cậy đo lường.
+- 1.0đ: Soạn thảo câu kết luận báo cáo chuẩn mực, khách quan và minh bạch về sự chênh lệch độ tin cậy.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phán quyết về Xếp hạng Chắc chắn: **TUYỆT ĐỐI KHÔNG ĐƯỢC PHÉP XẾP HẠNG CHẮC CHẮN (NO DEFINITIVE RANKING)**.
+- **Lập luận Toán học và Thống kê**:
+  + Phân khúc TP.HCM có $n = 70$: Kích thước mẫu đủ lớn, sai số chuẩn nhỏ, con số trung vị (median) có độ tin cậy thống kê cao.
+  + Phân khúc Hà Nội chỉ có $n = 8$: Đề bài nêu rõ quy chuẩn báo cáo đánh dấu $n &lt; 10$ là **Bất ổn định (Unstable)**.   Với chỉ vỏn vẹn 8 người trả lời, Khoảng tin cậy (Confidence Interval) của mức lương trung vị tại Hà Nội là cực kỳ rộng.   Chỉ cần 1 người trong nhóm 8 người đó thay đổi câu trả lời hoặc có mức lương đột biến (outlier), con số trung vị sẽ bị dịch chuyển dữ dội.
+- **Cạm bẫy 'Cùng Trung vị' (The Identical Median Fallacy)**: Việc hai ô có cùng một con số trung vị danh nghĩa (ví dụ đều là 50 triệu VNĐ) hoàn toàn không chứng minh được mức lương thực tế của hai thị trường là ngang nhau hay có thể xếp hạng ngang hàng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Ổn định Mẫu trong So sánh Phân đoạn (Sample Size Stability &amp; Segment Comparison): Một chỉ số thống kê chỉ có ý nghĩa khi đi kèm độ tin cậy của kích thước mẫu ($n$). So sánh một phân khúc vững chắc ($n=70$) với một phân khúc cực kỳ mong manh ($n=8$) rồi kết luận chắc chắn là ngụy biện khoa học. Viết kết luận đúng đòi hỏi phải nêu rõ sự bất ổn định của mẫu nhỏ và coi con số của Hà Nội chỉ là dữ liệu tham khảo bước đầu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+David Sheskin: Handbook of Parametric and Nonparametric Statistical Procedures &amp; U.S. Bureau of Labor Statistics (BLS) Standards for Data Reliability</t>
         </is>
       </c>
     </row>
@@ -938,10 +1013,33 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Dùng cấu trúc: evidence gợi ý gì, cho ai/khi nào, và chưa chứng minh gì.
-Phân tích theo nguyên lý thiết kế: Dùng cấu trúc: evidence gợi ý gì, cho ai/khi nào, và chưa chứng minh gì.</t>
+- 1.0đ: Trình bày chính xác bằng chứng quan sát thực nghiệm gợi ý điều gì (Senior quan tâm AI nhiều hơn Junior).
+- 1.0đ: Xác định rõ phạm vi áp dụng (người dùng nền tảng tuyển dụng 2025-2026).
+- 1.0đ: Phân tích thấu đáo điều bằng chứng CHƯA chứng minh (tương quan không phải nhân quả, thiếu randomization).
+- 1.0đ: Đưa ra kết luận hành động cân bằng, hữu ích cho quyết định học tập (học AI nhưng không bỏ rơi nền tảng cốt lõi).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Soạn thảo Suy luận có Giới hạn (Bounded Inference) cho Quyết định Học tập Hiện tại:
+```text
+BẢN GHI SUY LUẬN GIỚI HẠN (BOUNDED INFERENCE MEMO)
+1. BẰNG CHỨNG THỰC CHỨNG GỢI Ý ĐIỀU GÌ (What the Evidence Suggests):
+Dữ liệu khảo sát 2025–2026 từ nền tảng tuyển dụng chỉ ra một mối liên hệ quan sát được (observational association): 
+nhóm nhân sự cấp Senior có tỷ lệ tự báo cáo mức độ quan tâm và chủ động tìm hiểu công nghệ AI cao hơn rõ rệt so với nhóm Junior.
+2. PHẠM VI ÁP DỤNG CỤ THỂ (Applicable Scope):
+Áp dụng cho cộng đồng người dùng đang chủ động tìm việc hoặc cập nhật hồ sơ trên nền tảng tuyển dụng này trong giai đoạn 2025–2026.
+3. BẰNG CHỨNG TUYỆT ĐỐI CHƯA CHỨNG MINH ĐIỀU GÌ (What the Evidence Does NOT Prove):
+- KHÔNG CHỨNG MINH MỐI QUAN HỆ NHÂN QUẢ (Correlation != Causation): Khảo sát không có can thiệp ngẫu nhiên (Zero Randomization). 
+  Nó KHÔNG chứng minh rằng 'học AI sẽ tự động biến một Junior thành Senior', cũng KHÔNG chứng minh 'quan tâm AI là nguyên nhân giúp họ lên Senior'. 
+  Mối liên hệ này có thể bị chi phối bởi các biến số tiềm ẩn (như số năm kinh nghiệm, tư duy tự học sẵn có, hoặc áp lực giải quyết bài toán phức tạp của cấp Senior).
+- KHÔNG CHỨNG MINH JUNIOR KHÔNG CẦN AI: Khảo sát chỉ đo mức độ quan tâm chủ quan, không phản ánh yêu cầu kỹ năng bắt buộc tại các doanh nghiệp.
+4. KẾT LUẬN HÀNH ĐỘNG HỢP LÝ CHO QUYẾT ĐỊNH HỌC TẬP (Actionable Pragmatic Takeaway):
+Người học nên nhìn nhận kỹ năng AI như một 'Vũ khí Gia tăng Giá trị' (Value Multiplier) phù hợp với định hướng phát triển dài hạn của cấp Senior; 
+tuy nhiên, TUYỆT ĐỐI KHÔNG bỏ bê các nền tảng kỹ thuật cốt lõi (Data Structures, System Design, Clean Code) để chạy theo AI bề nổi, 
+bởi vì kiến thức nền tảng vững chắc mới là điều kiện tiên quyết để đạt tới đẳng cấp Senior.
+```
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Suy luận Bị Chặn trong Dữ liệu Quan sát (Bounded Inference &amp; Causal Distinctions): Một mối tương quan (Association) trong dữ liệu khảo sát không bao giờ được phép diễn giải thành quan hệ nhân quả (Causation). Sự thật là Senior quan tâm AI nhiều hơn, nhưng đó là vì họ có nền tảng vững và nhìn thấy bài toán ứng dụng. Một suy luận có trách nhiệm phải vạch rõ ranh giới 'chưa chứng minh điều gì' để giúp người học không đưa ra các quyết định học tập lệch lạc.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Judea Pearl: Causality: Models, Reasoning, and Inference &amp; Austin Bradford Hill: The Environment and Disease: Association or Causation?</t>
         </is>
       </c>
     </row>
@@ -972,10 +1070,35 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Correlation và duplicated template làm evidence hẹp.
-Phân tích theo nguyên lý thiết kế: Correlation và duplicated template làm evidence hẹp.</t>
+- 1.0đ: Nhận diện chính xác hạn chế dữ liệu: 3 JDs từ cùng 1 tập đoàn và dùng chung 1 template tuyển dụng.
+- 1.0đ: Xác lập phạm vi suy luận dùng được hợp lệ (chỉ có giá trị với tập đoàn cụ thể đó).
+- 1.0đ: Vạch trần và nghiêm cấm các tuyên bố thổi phồng toàn ngành (overclaims về cơn sốt RAG toàn cầu).
+- 1.0đ: Đưa ra kết luận hành động thực tế và đề xuất theo dõi đa nguồn độc lập trong thời gian dài hơn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Soạn thảo Bản ghi Suy luận Dùng được Không Thổi phồng (Bounded Inference without Overclaiming):
+```text
+BẢN GHI SUY LUẬN DỮ LIỆU TUYỂN DỤNG (RECRUITMENT DATA BOUNDED INFERENCE)
+1. SỰ THẬT QUAN SÁT KHÁCH QUAN (Objective Observed Fact):
+Trong tuần này, có 3 bản mô tả công việc (JDs) ghi nhận yêu cầu kỹ năng RAG (Retrieval-Augmented Generation). 
+Tuy nhiên, cả 3 JDs này đều xuất phát từ CÙNG MỘT TẬP ĐOÀN DOANH NGHIỆP (Single Company Group) 
+và sử dụng CHUNG MỘT KHUNG MẪU TUYỂN DỤNG (Identical Recruiter Template).
+2. PHẠM VI SUY LUẬN HỢP LỆ (Valid Scoped Inference):
+- Bằng chứng này xác nhận rằng tập đoàn cụ thể này đang có chiến lược mở rộng ứng dụng RAG hoặc đang tuyển dụng đồng loạt 
+  cho các dự án AI nội bộ của họ trong tuần này.
+- Nếu ứng viên có mục tiêu ứng tuyển vào tập đoàn này, kỹ năng RAG là yêu cầu bắt buộc cần chuẩn bị kỹ lưỡng.
+3. TUYÊN BỐ THỔI PHỒNG BỊ NGHIÊM CẤM (Forbidden Overclaims):
+- CẤM TUYÊN BỐ: 'Thị trường toàn ngành đang bùng nổ cơn sốt tuyển dụng RAG trong tuần này!'
+- CẤM TUYÊN BỐ: '100% các công ty công nghệ hiện nay đều bắt buộc phải biết RAG mới xin được việc.'
+- Lý do: Ba JD từ một công ty dùng chung template chỉ đại diện cho **1 quyết định nhân sự duy nhất** được nhân bản thành 3 bài đăng (Duplicated Template Artifact), 
+  hoàn toàn không mang tính đại diện thống kê cho toàn bộ thị trường lao động (Kích thước mẫu thực chất chỉ là $N_{\text{effective}} = 1$).
+4. KẾT LUẬN HÀNH ĐỘNG THỰC TẾ (Actionable Conclusion):
+Ghi nhận RAG là một kỹ năng có nhu cầu thực tế tại một số doanh nghiệp lớn; 
+tiếp tục theo dõi thị trường trên nhiều nhóm công ty độc lập khác nhau trong 4-8 tuần tiếp theo trước khi đưa ra nhận định về xu hướng chung của ngành.
+```
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Nhận diện Dữ liệu Trùng lặp trong Phân tích Thị trường (Duplicated Template Artifacts &amp; Effective Sample Size): Một cạm bẫy lớn trong phân tích dữ liệu tuyển dụng là đếm số lượng tin đăng bề mặt. Một công ty đăng 10 bài viết giống hệt nhau qua một headhunter template chỉ là 1 điểm dữ liệu duy nhất ($N=1$). Tuyên bố một xu hướng thị trường dựa trên các dữ liệu trùng lặp từ một nguồn đơn lẻ là hành vi thổi phồng nguy hiểm. Kỹ sư dữ liệu phải bóc tách số lượng mẫu thực tế để đưa ra kết luận chuẩn xác.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+David Freedman: Statistical Models: Theory and Practice &amp; Burning Glass Technologies Labor Market Analysis Standards</t>
         </is>
       </c>
     </row>
@@ -1058,10 +1181,32 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Ba source type không được ép cùng đo một biến.
-Phân tích theo nguyên lý thiết kế: Ba source type không được ép cùng đo một biến.</t>
+- 1.0đ: Phân tích chuẩn xác bằng chứng và vai trò riêng biệt của từng nguồn tin (Báo cáo vĩ mô, 3 JD vi mô, Portfolio audit).
+- 1.0đ: Không ép buộc 3 nguồn tin đo cùng một biến số mà nhìn thấy sự bổ trợ tam giác hóa logic.
+- 1.0đ: Chỉ ra lỗ hổng năng lực chí mạng giữa portfolio hiện tại (prompt demo) và yêu cầu thực tế (evaluation).
+- 1.0đ: Đưa ra quyết định học tập hành động cụ thể, dứt khoát (tập trung học Eval và xây dựng artifact benchmark).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Soạn thảo Bản Tổng hợp Đa Nguồn Chứng cứ (Claim-Evidence Synthesis) cho Quyết định Học tập:
+1. **Ma trận Tam giác hóa Dữ liệu Ba Nguồn Độc lập (Triangulation Matrix)**:
+- **Nguồn 1: Báo cáo Xu hướng Vĩ mô (Macro Industry Report)**:
+  + *Bằng chứng*: Báo cáo chỉ ra mức độ quan tâm và nhu cầu đối với kỹ năng AI nói chung đang tăng trưởng mạnh mẽ.
+  + *Vai trò*: Khẳng định đây là một miền công nghệ giàu tiềm năng dài hạn, đáng để đầu tư thời gian.
+- **Nguồn 2: Dữ liệu Tuyển dụng Cụ thể Vi mô (Micro Target-Role JDs)**:
+  + *Bằng chứng*: 3 bản mô tả công việc của đúng vai trò mục tiêu (Target Role) đều yêu cầu rõ kỹ năng **Evaluation (Đánh giá, Kiểm chuẩn, Đo lường Chất lượng AI)**.
+  + *Vai trò*: Xác lập yêu cầu kỹ thuật cụ thể bắt buộc cần có để vượt qua vòng phỏng vấn thực tế của nhà tuyển dụng.
+- **Nguồn 3: Kiểm toán Năng lực Hồ sơ Cá nhân (Personal Portfolio Audit)**:
+  + *Bằng chứng*: Portfolio hiện tại chỉ có các demo gọi prompt đơn giản (Prompt Demo) mà **HOÀN TOÀN KHÔNG CÓ BẤT KỲ DỰ ÁN NÀO VỀ EVALUATION / BENCHMARKING**.
+  + *Vai trò*: Chỉ ra lỗ hổng năng lực (Skill Gap) chí mạng giữa những gì mình đang có và những gì nhà tuyển dụng đang tìm kiếm.
+2. **Tổng hợp Luận điểm và Quyết định Học tập Hành động (Actionable Synthesis &amp; Decision)**:
+- **Tuyên bố Luận điểm Tổng hợp (Synthesized Claim)**: 'Mặc dù thị trường hào hứng với AI nói chung (Nguồn 1), nhưng các nhà tuyển dụng thực tế không tìm kiếm người chỉ biết viết prompt đơn giản; họ tìm kiếm kỹ sư có năng lực đo lường và đánh giá chất lượng hệ thống (Nguồn 2). Portfolio hiện tại đang có sự lệch pha nghiêm trọng so với nhu cầu tuyển dụng thực tế (Nguồn 3).'
+- **Quyết định Học tập Ưu tiên Tuyệt đối (Actionable Decision)**:
+  + **DỪNG LẠI**: Ngừng xây dựng thêm các ứng dụng demo prompt đồ chơi bề nổi.
+  + **TẬP TRUNG HỌC NGAY**: Dành 100% thời gian học tập trong 4 tuần tới vào **Phương pháp luận Đánh giá AI (AI Evaluation Frameworks)**:   Ragas, TruLens, LLM-as-a-Judge, thiết kế Golden Benchmark, và xây dựng CI/CD testing pipeline.
+  + **XÂY DỰNG ARTIFACT MỤC TIÊU**: Nâng cấp portfolio bằng cách xuất bản một dự án thực tế: 'Hệ thống Đánh giá và Đo lường Độ tin cậy cho Chatbot Doanh nghiệp kèm Báo cáo Hồi quy'.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Tam giác hóa Nguồn tin trong Hoạch định Nghề nghiệp (Cross-source Triangulation in Career Decisions): Ba nguồn tin không đo cùng một biến số nhưng bổ trợ hoàn hảo cho nhau: Báo cáo thị trường cho biết hướng đi của dòng chảy (Vector hướng); JD tuyển dụng cho biết chiếc chìa khóa qua cửa (Tiêu chuẩn kỹ thuật); và Portfolio cho biết vị trí hiện tại của bản thân. Tổng hợp ba nguồn tin giúp người học thoát khỏi ảo tưởng 'chỉ cần biết viết prompt là xin được việc' và tập trung vào kỹ năng Evaluation có giá trị tuyển dụng cao nhất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Norman K. Denzin: The Research Act: A Theoretical Introduction to Sociological Methods (Triangulation Methodology)</t>
         </is>
       </c>
     </row>
@@ -1092,10 +1237,25 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng thay mô tả công việc bằng danh sách technology.
-Phân tích theo nguyên lý thiết kế: Đừng thay mô tả công việc bằng danh sách technology.</t>
+- 1.0đ: Vượt khỏi nhãn chức danh, nắm bắt đúng bản chất vai trò là kỹ sư tác chiến tiền tuyến (field solutions engineer).
+- 1.0đ: Xác định rõ ràng các kết quả nghiệp vụ bắt buộc: tích hợp workflow logistics và đo lường business outcome.
+- 1.0đ: Phân định ranh giới dứt khoát: đây KHÔNG PHẢI vai trò nghiên cứu mô hình mới trong phòng lab.
+- 1.0đ: Chỉ ra năng lực cốt lõi cần có (giao tiếp khách hàng, chuyển hóa nỗi đau vận hành thành giải pháp AI thực chiến).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Tóm tắt Vai trò Mục tiêu Vượt khỏi Chức danh (Target Role Outcome Summary beyond Title) cho 'Forward Deployed AI Engineer':
+1. **Bản chất Cốt lõi của Vai trò (Core Role Mission)**:
+- Chức danh 'Forward Deployed AI Engineer' (FDAIE) không phải là một nhà nghiên cứu lý thuyết trong phòng lab. Bản chất đây là một **Kỹ sư Tác chiến Tiền tuyến (Field Solutions Engineer)** đóng vai trò là cầu nối trực tiếp giữa công nghệ AI tiên tiến và hiện trường sản xuất kinh doanh của khách hàng (ngành logistics).
+2. **Các Kết quả Nghiệp vụ Bắt buộc Cần Chuyển giao (Business Outcome Contracts)**:
+- **Tích hợp Quy trình Vận hành Thực tế (Workflow Integration)**: Nhúng các mô hình AI vào quy trình xử lý đơn hàng, điều phối kho bãi và tối ưu hóa tuyến đường vận tải hiện hữu của khách hàng logistics.
+- **Đo lường và Chịu trách nhiệm về Chỉ số Kinh doanh (Business Outcome Delivery)**: Thành công của vai trò này không đo bằng độ chính xác lý thuyết (Loss/F1), mà đo bằng các chỉ số kinh doanh thực tế: giảm 15% thời gian xử lý đơn hàng logistics, giảm 20% chi phí điều phối xe, hoặc giảm tỷ lệ giao hàng trễ hạn.
+- **Tương tác Khách hàng Trực tiếp (Customer Empathy &amp; Requirement Engineering)**: Làm việc trực tiếp với các giám đốc kho, nhân viên logistics để lắng nghe nỗi đau vận hành, thu thập phản hồi và tùy biến giải pháp AI tại chỗ.
+3. **Ranh giới Phân định Rõ ràng (What this Role is NOT)**:
+- **KHÔNG PHẢI Research Scientist**: JD hoàn toàn không yêu cầu nghiên cứu phát minh kiến trúc mô hình mới (novel foundation model research) hay huấn luyện pre-training từ đầu.
+- **KHÔNG PHẢI Generic Web Developer**: Vai trò đòi hỏi hiểu biết sâu sắc về tích hợp mô hình, xử lý rủi ro ảo giác của LLM và tối ưu hóa hiệu năng ứng dụng trong môi trường thực địa.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Định nghĩa Vai trò Dựa trên Kết quả (Outcome-based Role Definition vs Title Inflation): Các chức danh AI hiện đại thường bị 'thổi phồng' (Title Inflation). Một Forward Deployed AI Engineer tại Palantir hay các startup logistics thực chất là người giải quyết bài toán kinh doanh cho khách hàng bằng công nghệ AI có sẵn. Nhận thức rõ ranh giới này giúp ứng viên tập trung chuẩn bị các kỹ năng thực chiến (System Integration, Business Metrics, Customer Communication) thay vì lãng phí thời gian vào việc học đạo hàm huấn luyện model trong phòng thí nghiệm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Palantir Technologies: The Forward Deployed Software Engineer Philosophy &amp; Pragmatic Engineer: Role Archetypes</t>
         </is>
       </c>
     </row>
@@ -1126,10 +1286,27 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Role title là entrypoint, không phải đầy đủ outcome contract.
-Phân tích theo nguyên lý thiết kế: Role title là entrypoint, không phải đầy đủ outcome contract.</t>
+- 1.0đ: Khẳng định chức danh chỉ là điểm vào ban đầu (entrypoint), không phải hợp đồng kết quả cố định.
+- 1.0đ: Phân tích sâu sắc bản chất Biến thể JD1 (Retail Startup Junior: thiên về customer integration, application layer).
+- 1.0đ: Phân tích sâu sắc bản chất Biến thể JD2 (Cloud Vendor Senior: thiên về model platform, infrastructure systems).
+- 1.0đ: Xây dựng bảng so sánh đa chiều và đưa ra định hướng lựa chọn nghề nghiệp chuẩn xác dựa trên thế mạnh cá nhân.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Soạn thảo Bản Tóm tắt Vai trò Mục tiêu Bảo toàn Sự Biến thiên (Target-Role Summary Preserving Variation) cho 'AI Product Engineer':
+1. **Bản chất của Điểm vào Chức danh (Title as an Entrypoint, Not a Fixed Contract)**:
+Cùng mang chức danh 'AI Product Engineer', nhưng JD1 (tại Retail Startup) và JD2 (tại Cloud Vendor) đại diện cho hai thực tại nghề nghiệp hoàn toàn khác nhau. Một bản tóm tắt vai trò chuyên nghiệp không được phép cào bằng mà phải giữ nguyên vẹn sự biến thiên cấu trúc (Structural Variation).
+2. **Bảng Phân tích Biến thiên Cấu trúc Giữa Hai Vai trò (Comparative Variation Matrix)**:
+| Tiêu chí So sánh | Biến thể A: Retail Startup (JD1 - Junior) | Biến thể B: Cloud Vendor (JD2 - Senior) |
+| :--- | :--- | :--- |
+| **Trọng tâm Nghiệp vụ (Core Mission)** | **Tích hợp Khách hàng &amp; Ứng dụng Bán lẻ (Customer Integration)**: Tích hợp mô hình AI vào luồng mua sắm, giỏ hàng, tư vấn sản phẩm bán lẻ. | **Hạ tầng Nền tảng Mô hình (Model Platform Engineering)**: Xây dựng nền tảng phục vụ hàng nghìn mô hình cho các nhà phát triển bên ngoài. |
+| **Tầng Kiến trúc Công nghệ (Stack Layer)** | **Application &amp; UX Layer**: Prompt engineering, gọi API có sẵn, xử lý frontend/backend ứng dụng, tích hợp CRM/Shopify. | **Systems &amp; Infrastructure Layer**: Tối ưu hóa throughput, distributed inference serving, latency vLLM/Triton, multi-tenancy quotas. |
+| **Cấp độ Năng lực &amp; Kỳ vọng (Seniority)** | **Junior Level**: Cần sự nhanh nhẹn, khéo léo triển khai tính năng theo user story, học hỏi nhanh công cụ mới. | **Senior Level**: Đòi hỏi kiến trúc hệ thống quy mô lớn (High Scalability), bảo mật hạ tầng và dẫn dắt kỹ thuật. |
+| **Chỉ số Đo lường Thành công** | Tỷ lệ chuyển đổi mua hàng (Conversion Rate), trải nghiệm người dùng cuối. | Độ sẵn sàng hệ thống 99.99%, P99 inference latency, chi phí vận hành máy chủ. |
+3. **Kết luận Định hướng Nghề nghiệp (Pragmatic Strategy)**:
+Ứng viên khi ứng tuyển chức danh 'AI Product Engineer' bắt buộc phải đọc sâu vào bản chất công việc: nếu thế mạnh là hiểu sản phẩm và làm nhanh giao diện người dùng, hãy chọn Biến thể A (Startup); nếu thế mạnh là hệ thống phân tán và hạ tầng kỹ thuật sâu, hãy chọn Biến thể B (Cloud Vendor).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Bảo toàn Biến thiên trong Phân tích Nghề nghiệp (Preserving Variation in Role Archetypes): Trong thị trường lao động AI mới nổi, cùng một chức danh có thể được dùng cho hai công việc trái ngược 180 độ. Ép chung hai JD vào một định nghĩa 'trung bình' sẽ làm mất toàn bộ giá trị định hướng. Bảo toàn sự khác biệt giữa tầng Ứng dụng (Application/Customer layer) và tầng Nền tảng (Platform/Infra layer) giúp ứng viên định vị đúng năng lực bản thân với kỳ vọng thực tế của nhà tuyển dụng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Pragmatic Engineer: Software Engineer Archetypes &amp; The AI Product Engineer Emergence (Gergely Orosz, 2024)</t>
         </is>
       </c>
     </row>
@@ -1214,10 +1391,30 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Sampling quyết định claim population.
-Phân tích theo nguyên lý thiết kế: Sampling quyết định claim population.</t>
+- 1.0đ: Thiết kế Mẫu chính chuẩn mực chỉ gồm Posting 1 (khớp 100% cả role, level junior và geography).
+- 1.0đ: Khẳng định nguyên tắc liêm chính dữ liệu: tuyệt đối không bịa đặt thêm tin tuyển dụng giả.
+- 1.0đ: Thiết kế Mẫu nhạy cảm 1 (Senior local) để phân tích lộ trình thăng tiến kỹ năng.
+- 1.0đ: Thiết kế Mẫu nhạy cảm 2 (Junior quốc tế) để đối chiếu chuẩn mực năng lực toàn cầu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Mẫu Chính (Primary Sample) và Mẫu Nhạy cảm (Sensitivity Sample) từ 6 Tin Tuyển dụng Thực tế (Không Bịa đặt Dữ liệu):
+1. **Bản đồ Phân loại Hiện trạng 6 Tin Tuyển dụng Thực tế**:
+- Posting 1: Đúng vai trò mục tiêu + Cấp Junior + Địa lý mục tiêu hiện tại (Local) -&gt; **MẪU KHỚP TUYỆT ĐỐI 100%**.
+- Posting 2 &amp; 3 (2 postings): Đúng vai trò mục tiêu + Địa lý mục tiêu (Local), nhưng cấp độ là **Senior**.
+- Posting 4, 5, 6 (3 postings): Đúng vai trò mục tiêu + Cấp Junior, nhưng nằm ở **Quốc gia khác (International)**.
+2. **Thiết kế Mẫu Chính (Primary Sample - Nghiêm ngặt về Quần thể Mục tiêu)**:
+- **Thành phần Mẫu Chính**: Chỉ duy nhất **Posting 1** ($N_{\text{primary}} = 1$).
+- **Lập luận Phương pháp luận**: Nguyên tắc liêm chính dữ liệu nghiêm cấm việc bịa thêm tin tuyển dụng giả để cho 'đủ số lượng'. Khi quần thể tuyển dụng thực tế tại địa phương cho vị trí Junior chỉ có đúng 1 tin đăng, chúng ta bắt buộc phải thừa nhận thực tế đó. Posting 1 phản ánh chính xác 100% yêu cầu tuyển dụng thực tế tại thị trường địa phương của mình lúc này.
+3. **Thiết kế Mẫu Nhạy cảm (Sensitivity Analysis Samples - Mở rộng Ranh giới có Kiểm soát)**:
+- Để kiểm tra xem các kỹ năng yêu cầu trong Posting 1 có phải là cá biệt hay không, thiết lập 2 mẫu độ nhạy bổ trợ:
+- **Mẫu Nhạy cảm 1 (Local Senior Horizon - Posting 2 &amp; 3, $n=2$)**:
+  + *Mục đích*: Phân tích khoảng cách kỹ năng (Skill Gap Progression). So sánh xem cấp Senior tại địa phương yêu cầu thêm những kỹ năng gì so với Posting 1,   từ đó giúp ứng viên biết trước lộ trình thăng tiến trong 2-3 năm tới.
+- **Mẫu Nhạy cảm 2 (Global Junior Benchmark - Posting 4, 5, 6, $n=3$)**:
+  + *Mục đích*: Đo lường chuẩn mực quốc tế (Global Competitiveness). So sánh xem kỹ năng Junior ở nước ngoài có đòi hỏi cao hơn hoặc khác biệt gì so với Posting 1 nội địa hay không.
+- **Kết luận Báo cáo**: Tuyên bố rõ ràng: Mẫu chính có $N=1$, được kiểm chứng độ nhạy qua 2 tin Senior nội địa và 3 tin Junior quốc tế.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thiết kế Mẫu Tuyển dụng và Phân tích Độ nhạy (Primary Sampling &amp; Sensitivity Analysis in Job Market Research): Trong nghiên cứu thực nghiệm, sự khan hiếm dữ liệu thực tế là điều thường xuyên xảy ra. Hành vi tự bịa thêm tin tuyển dụng là gian lận khoa học. Kỹ thuật chuẩn mực là sử dụng một mẫu chính cực kỳ chặt chẽ (Posting 1), sau đó sử dụng các mẫu mở rộng có phân loại (Senior và Quốc tế) như các phép kiểm tra độ nhạy (Sensitivity checks) để rút ra bức tranh nghề nghiệp toàn diện mà vẫn giữ vững tính trung thực của dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+David Freedman: Statistical Models and Causal Inference &amp; Labor Market Sampling Methodologies</t>
         </is>
       </c>
     </row>
@@ -1296,10 +1493,31 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Ghi frequency cùng locator, rồi giải thích threshold recurring.
-Phân tích theo nguyên lý thiết kế: Ghi frequency cùng locator, rồi giải thích threshold recurring.</t>
+- 1.0đ: Trích xuất và lập bảng đầy đủ tần suất của toàn bộ 5 kỹ năng kèm mẫu số 3 JDs.
+- 1.0đ: Mã hóa chuẩn xác nhóm Recurring (Python 3/3, SQL 3/3, Airflow 2/3) dựa trên ngưỡng $\ge 2/3$.
+- 1.0đ: Mã hóa chuẩn xác nhóm Exception (dbt 1/3, AWS 1/3) chỉ rõ tính chất đặc thù của công ty đơn lẻ.
+- 1.0đ: Lưu giữ đầy đủ thông tin nguồn gốc (Provenance: company name, date) cho từng dòng mã hóa.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Mã hóa Yêu cầu Lặp lại và Ngoại lệ (Recurring Requirements &amp; Exceptions Coding) Bảo toàn Nguồn gốc Dữ liệu (Provenance):
+1. **Bảng Trích xuất Kỹ năng Kèm Mã Định vị Nguồn gốc (Provenance Mapping)**:
+- **JD1**: `Python`, `SQL`, `Airflow` | *Locator*: `company=LogisticsCorp_A`, `date=2026-10-01`.
+- **JD2**: `Python`, `SQL`, `dbt`     | *Locator*: `company=RetailEcom_B`,    `date=2026-10-05`.
+- **JD3**: `Python`, `SQL`, `Airflow`, `AWS` | *Locator*: `company=FintechApp_C`, `date=2026-10-12`.
+- Tổng số bản mô tả công việc phân tích: $N_{\text{total}} = 3$ JDs.
+- **Quy ước kỹ thuật**: Một yêu cầu được coi là Lặp lại (Recurring) nếu tần suất xuất hiện $\ge 2/3$ JDs (tương ứng $\ge 66.7\%$).
+2. **Mã hóa Kết quả Phân loại Kỹ năng (Structured Requirement Coding)**:
+| Nhóm Phân loại | Kỹ năng Mã hóa | Tần suất Thực tế | Tỷ lệ (%) | Mã Định vị Nguồn gốc (Provenance Locators) | Kết luận Đánh giá |
+| :--- | :--- | :--- | :--- | :--- | :--- |
+| **RECURRING (Bắt buộc Lặp lại)** | **Python** | 3 / 3 JDs | 100% | Xuất hiện ở JD1, JD2, JD3 | **Kỹ năng Cốt lõi Tuyệt đối (Core Mandatory)**: 100% nhà tuyển dụng yêu cầu. |
+| **RECURRING (Bắt buộc Lặp lại)** | **SQL** | 3 / 3 JDs | 100% | Xuất hiện ở JD1, JD2, JD3 | **Kỹ năng Cốt lõi Tuyệt đối (Core Mandatory)**: Truy vấn dữ liệu là yêu cầu phổ quát. |
+| **RECURRING (Lặp lại Chuyên ngành)** | **Airflow** | 2 / 3 JDs | 66.7% | Xuất hiện ở JD1 (Logistics) và JD3 (Fintech) | **Kỹ năng Tiêu chuẩn Ngành (Standard Workflow Tool)**: Đạt ngưỡng $\ge 2/3$. |
+| **EXCEPTION (Ngoại lệ Doanh nghiệp)** | **dbt** | 1 / 3 JDs | 33.3% | Chỉ xuất hiện duy nhất tại JD2 (RetailEcom_B) | **Ngoại lệ Ngăn xếp Riêng (Company Stack Specific)**: Dưới ngưỡng $2/3$. |
+| **EXCEPTION (Ngoại lệ Doanh nghiệp)** | **AWS** | 1 / 3 JDs | 33.3% | Chỉ xuất hiện duy nhất tại JD3 (FintechApp_C) | **Ngoại lệ Hạ tầng Đám mây Cụ thể**: Dưới ngưỡng $2/3$. |
+3. **Kết luận Chiến lược Cho Ứng viên**: Tập trung 90% thời gian rèn luyện làm chủ bộ ba `Python + SQL + Airflow` để đáp ứng yêu cầu của đại đa số nhà tuyển dụng; `dbt` và `AWS` chỉ học bổ trợ khi nhắm mục tiêu cụ thể vào công ty B hoặc C.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Mã hóa Dữ liệu Tuyển dụng có Nguồn gốc (Requirement Coding with Provenance): Một sai lầm phổ biến khi đọc JD là biến mọi từ khóa xuất hiện thành danh sách kỹ năng bắt buộc phải học, dẫn đến việc người học bị quá tải trước ma trận công nghệ. Bằng cách thiết lập ngưỡng lặp lại rõ ràng ($\ge 2/3$) và lưu giữ mã định vị (Provenance Locators: công ty nào, ngày nào), kỹ sư phân biệt được đâu là kỹ năng nền tảng phổ quát của thị trường (Python/SQL/Airflow) và đâu chỉ là công nghệ đặc thù cục bộ của một công ty đơn lẻ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Content Analysis Methodologies (Krippendorff, 2018) &amp; Data Engineering Job Market Skill Coding Standards</t>
         </is>
       </c>
     </row>
@@ -1330,10 +1548,32 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Alternative wording phải được code theo context, không keyword-only.
-Phân tích theo nguyên lý thiết kế: Alternative wording phải được code theo context, không keyword-only.</t>
+- 1.0đ: Trình bày đầy đủ mẫu số chuẩn xác cho toàn bộ các kỹ năng trên tổng số 4 JDs ($N=4$).
+- 1.0đ: Mã hóa chuẩn xác SQL (4/4 Hard Mandatory) và Spark (2/4 Recurring Big Data Framework).
+- 1.0đ: Bóc tách sắc thái ngữ nghĩa của Python và Java (Python 3/4 hard + 1/4 alternative; Java là alternative option).
+- 1.0đ: Phân tích thấu đáo rủi ro của việc đếm từ khóa cơ học (keyword-only) bỏ qua ngữ cảnh liên từ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Mã hóa Yêu cầu Tuyển dụng Có Mẫu số và Bóc tách Sắc thái Ngôn từ (Requirement Coding with Denominator &amp; Nuance):
+1. **Bản đồ Trích xuất Dữ liệu Gốc từ 4 JDs ($N = 4$)**:
+- JD1: SQL (Bắt buộc), Python (Bắt buộc), Spark, Kubernetes.
+- JD2: SQL (Bắt buộc), Python (Bắt buộc), Spark.
+- JD3: SQL (Bắt buộc), Python (Bắt buộc).
+- JD4: SQL (Bắt buộc), 'Python HOẶC Java' (Chấp nhận thay thế tương đương).
+- **Quy ước kỹ thuật**: Ngưỡng lặp lại (Recurring Threshold) là xuất hiện ở ít nhất 2 JDs ($\ge 2/4$). Yêu cầu bắt buộc tuyệt đối (Mandatory) và Lựa chọn thay thế tương đương (Alternative Nuance) bắt buộc phải được mã hóa ở hai trường độc lập.
+2. **Bảng Mã hóa Bóc tách Sắc thái Kỹ năng (Nuanced Requirement Coding Table)**:
+| Kỹ năng / Cụm Kỹ năng | Tần suất Bắt buộc Tuyệt đối (Hard Mandatory) | Tần suất Lựa chọn Thay thế (Alternative Option) | Tổng Độ bao phủ (Total Coverage) | Phân loại Chuẩn mực (Classification) |
+| :--- | :--- | :--- | :--- | :--- |
+| **SQL** | **4 / 4 JDs (100%)** | 0 / 4 | **4 / 4 (100%)** | **RECURRING HARD MANDATORY**: Kỹ năng bắt buộc tuyệt đối 100%, không có ngoại lệ. |
+| **Python** | **3 / 4 JDs (75%)** | **1 / 4 JDs (25% - thay bằng Java)** | **4 / 4 (100%)** | **RECURRING CORE LANGUAGE (WITH ALTERNATIVE NUANCE)**: 3 nơi bắt buộc cứng, 1 nơi chấp nhận Java. Vẫn đạt ngưỡng Recurring. |
+| **Java** | 0 / 4 JDs (0%) | **1 / 4 JDs (25% - thay thế cho Python)** | 1 / 4 (25%) | **ALTERNATIVE EXCEPTION**: Không phải ngôn ngữ chính, chỉ là lựa chọn thay thế cục bộ tại JD4. |
+| **Apache Spark** | **2 / 4 JDs (50%)** | 0 / 4 | **2 / 4 (50%)** | **RECURRING BIG DATA FRAMEWORK**: Đạt ngưỡng Recurring (2/4 JDs), là kỹ năng quan trọng. |
+| **Kubernetes** | **1 / 4 JDs (25%)** | 0 / 4 | **1 / 4 (25%)** | **NICHE INFRASTRUCTURE EXCEPTION**: Dưới ngưỡng 2/4, chỉ là yêu cầu riêng của JD1. |
+3. **Phân tích Sắc thái Kỹ thuật (Contextual Nuance Analysis)**:
+- Nếu chỉ đếm từ khóa cơ học (Keyword-only count), người phân tích sẽ nhầm lẫn: ghi nhận Java là một yêu cầu độc lập (1/4) và coi Python chỉ đạt 3/4. Thực tế phân tích ngữ cảnh chỉ ra: Cả 4 JD đều đòi hỏi một **Ngôn ngữ Lập trình Hướng đối tượng Mạnh** (Backend Programming Language = 4/4), trong đó Python là lựa chọn áp đảo (3/4 bắt buộc, 1/4 chấp nhận Java thay thế). Việc bóc tách trường 'Alternative' bảo đảm ứng viên hiểu đúng: biết Java vẫn có thể nộp được vào JD4 nhưng không nộp được vào JD1-3.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Phân tích Ngữ cảnh trong Mã hóa JD (Contextual Nuance vs Keyword-Only Matching): Bộ máy lọc CV tự động (ATS) thường mắc lỗi ngớ ngẩn khi đếm từ khóa: bỏ qua các liên từ logic như 'HOẶC' (OR / Alternative). Một quy trình nghiên cứu thị trường chuẩn mực phải bóc tách giữa 'Bắt buộc cứng' (Hard Mandatory) và 'Lựa chọn thay thế' (Alternative). Ghi nhận mẫu số đầy đủ (4/4, 3/4) và sắc thái ngôn từ giúp xây dựng hồ sơ năng lực chính xác tuyệt đối.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Klaus Krippendorff: Content Analysis: An Introduction to Its Methodology &amp; Natural Language Processing for Recruitment Analytics</t>
         </is>
       </c>
     </row>
